--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -477,20 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>105,386</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Garmin</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -507,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +538,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Total Points</t>
         </is>
       </c>
@@ -539,6 +559,9 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -552,6 +575,9 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +589,9 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>105386</v>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -582,6 +611,11 @@
           <t>---</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -593,6 +627,9 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>105386</v>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
     </row>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -440,25 +440,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Image Link</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -589,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>105386</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -627,10 +617,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>105386</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -579,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>105386</v>
       </c>
       <c r="D4" t="n">
-        <v>105386</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -617,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>105386</v>
       </c>
       <c r="D6" t="n">
-        <v>105386</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -592,7 +592,7 @@
         <v>105386</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>105386</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,53 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6/2/2026 15:45:53</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9,725</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Healthy 365</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -589,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>105386</v>
+        <v>115111</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -627,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>105386</v>
+        <v>115111</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,53 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:45:53</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>51,942</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -589,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>105386</v>
+        <v>157328</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -627,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>105386</v>
+        <v>157328</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/Reports/Members/Surya_Activity_Report.xlsx
+++ b/Reports/Members/Surya_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:51:47</t>
+          <t>2026-06-02 15:45:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>51,942</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-02 15:45:53</t>
+          <t>2026-05-19 11:51:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>51,942</t>
+          <t>105,386</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -555,6 +555,53 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6/8/2026 11:26:59</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,204</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -636,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>157328</v>
+        <v>161532</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -674,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>157328</v>
+        <v>161532</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
